--- a/Datasets/Malvinas/Nongeo/poblacion_malvinas.xlsx
+++ b/Datasets/Malvinas/Nongeo/poblacion_malvinas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATOS-HHD\Proyectos R\Malvinas\Datasets\Malvinas\Nongeo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC35A308-D104-4365-A92E-E521CDCADE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24A0FE6-3382-4E85-9D03-C92FDD154556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{D58B7E7A-44E9-45FD-BFBF-C90515DDD1A0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="122">
   <si>
     <t>Year</t>
   </si>
@@ -402,13 +402,16 @@
   </si>
   <si>
     <t>2,740,213,792</t>
+  </si>
+  <si>
+    <t>Elaboration of data by United Nations, Department of Economic and Social Affairs, Population Division. World Population Prospects: The 2024 Revision. (Medium-fertility variant).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -424,16 +427,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -441,26 +458,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -793,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E7DA666-161D-4D92-807F-A003A58B8977}">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
@@ -801,47 +836,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2026</v>
       </c>
@@ -882,7 +917,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2025</v>
       </c>
@@ -923,7 +958,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2024</v>
       </c>
@@ -964,7 +999,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2023</v>
       </c>
@@ -1005,7 +1040,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2022</v>
       </c>
@@ -1046,7 +1081,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -1128,7 +1163,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>2010</v>
       </c>
@@ -1169,7 +1204,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2005</v>
       </c>
@@ -1333,7 +1368,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>1985</v>
       </c>
@@ -1374,7 +1409,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>1980</v>
       </c>
@@ -1415,7 +1450,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>1975</v>
       </c>
@@ -1456,7 +1491,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1970</v>
       </c>
@@ -1497,7 +1532,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>1965</v>
       </c>
@@ -1579,7 +1614,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>1955</v>
       </c>
@@ -1620,7 +1655,15 @@
         <v>2</v>
       </c>
     </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A27" r:id="rId1" display="https://population.un.org/wpp/" xr:uid="{4CD66F37-CA99-4068-9DAC-96DCF88D6734}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>